--- a/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/practice_completed.xlsx
+++ b/datasets/day1_excel_foundations/07_tables_conditional_formatting_charts/practice_completed.xlsx
@@ -685,8 +685,8 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
